--- a/設計書/02.テーブル設計書/コード値一覧.xlsx
+++ b/設計書/02.テーブル設計書/コード値一覧.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yu-fujii\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yu-fujii\Desktop\設計書\設計書\02.テーブル設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9384" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9384"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="59">
   <si>
     <t>作成日</t>
     <rPh sb="0" eb="2">
@@ -270,6 +270,34 @@
     <t>解散</t>
     <rPh sb="0" eb="2">
       <t>カイサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>性別</t>
+    <rPh sb="0" eb="2">
+      <t>セイベツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>不明</t>
+    <rPh sb="0" eb="2">
+      <t>フメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>男</t>
+    <rPh sb="0" eb="1">
+      <t>オトコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>女</t>
+    <rPh sb="0" eb="1">
+      <t>オンナ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -493,7 +521,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -506,33 +534,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -554,19 +555,55 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -587,13 +624,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -636,8 +667,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -932,55 +963,55 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="6"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="17"/>
       <c r="O2" s="3"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="9"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="20"/>
       <c r="O3" s="3"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="12"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="23"/>
       <c r="O4" s="3"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
@@ -1349,10 +1380,10 @@
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
-      <c r="M26" s="13" t="s">
+      <c r="M26" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="N26" s="14">
+      <c r="N26" s="5">
         <v>45352</v>
       </c>
       <c r="O26" s="3"/>
@@ -1370,10 +1401,10 @@
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
-      <c r="M27" s="13" t="s">
+      <c r="M27" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="N27" s="13" t="s">
+      <c r="N27" s="4" t="s">
         <v>2</v>
       </c>
       <c r="O27" s="3"/>
@@ -1391,31 +1422,31 @@
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
-      <c r="M28" s="15" t="s">
+      <c r="M28" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="N28" s="13" t="str">
+      <c r="N28" s="4" t="str">
         <f>INDEX([1]改版履歴!D2:D31,COUNTA([1]改版履歴!D2:D31))</f>
         <v>24.0.1</v>
       </c>
       <c r="O28" s="3"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A29" s="16"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
-      <c r="M29" s="17"/>
-      <c r="N29" s="17"/>
-      <c r="O29" s="18"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1429,13 +1460,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:D46"/>
+  <dimension ref="A2:D51"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.5546875" style="21" customWidth="1"/>
+    <col min="1" max="1" width="17.5546875" style="11" customWidth="1"/>
     <col min="2" max="2" width="15.109375" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" style="19" customWidth="1"/>
-    <col min="4" max="4" width="26.5546875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" style="10" customWidth="1"/>
+    <col min="4" max="4" width="26.5546875" style="10" customWidth="1"/>
     <col min="5" max="5" width="11.88671875" customWidth="1"/>
     <col min="6" max="6" width="12.5546875" customWidth="1"/>
     <col min="7" max="7" width="17.5546875" customWidth="1"/>
@@ -1445,452 +1476,496 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="12" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="32">
+      <c r="C3" s="13">
         <v>1</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="13" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="29"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="32">
+      <c r="A4" s="32"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="13">
         <v>2</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="13" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="29"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="32">
+      <c r="A5" s="32"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="13">
         <v>3</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="13" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="29"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="32">
+      <c r="A6" s="32"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="13">
         <v>4</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="13" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="29"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="32">
+      <c r="A7" s="32"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="13">
         <v>5</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="D7" s="13" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="29"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="32">
+      <c r="A8" s="32"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="13">
         <v>6</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="13" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="29"/>
-      <c r="B9" s="26"/>
-      <c r="C9" s="32">
+      <c r="A9" s="32"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="13">
         <v>7</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" s="13" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="30"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="32">
+      <c r="A10" s="33"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="13">
         <v>8</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="13" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C12" s="31" t="s">
+      <c r="C12" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="31" t="s">
+      <c r="D12" s="12" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="13">
         <v>1</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="D13" s="13" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="29"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="32">
+      <c r="A14" s="32"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="13">
         <v>2</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="13" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="29"/>
-      <c r="B15" s="26"/>
-      <c r="C15" s="32">
+      <c r="A15" s="32"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="13">
         <v>3</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="13" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="29"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="32">
+      <c r="A16" s="32"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="13">
         <v>4</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="13" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="29"/>
-      <c r="B17" s="26"/>
-      <c r="C17" s="32">
+      <c r="A17" s="32"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="13">
         <v>5</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D17" s="13" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="29"/>
-      <c r="B18" s="26"/>
-      <c r="C18" s="32">
+      <c r="A18" s="32"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="13">
         <v>6</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="29"/>
-      <c r="B19" s="26"/>
-      <c r="C19" s="32">
+      <c r="A19" s="32"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="13">
         <v>7</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="13" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="29"/>
-      <c r="B20" s="26"/>
-      <c r="C20" s="32">
+      <c r="A20" s="32"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="13">
         <v>8</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="13" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="29"/>
-      <c r="B21" s="26"/>
-      <c r="C21" s="32">
+      <c r="A21" s="32"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="13">
         <v>9</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D21" s="13" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="29"/>
-      <c r="B22" s="26"/>
-      <c r="C22" s="32">
+      <c r="A22" s="32"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="13">
         <v>10</v>
       </c>
-      <c r="D22" s="32" t="s">
+      <c r="D22" s="13" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="29"/>
-      <c r="B23" s="26"/>
-      <c r="C23" s="32">
+      <c r="A23" s="32"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="13">
         <v>11</v>
       </c>
-      <c r="D23" s="32" t="s">
+      <c r="D23" s="13" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="29"/>
-      <c r="B24" s="26"/>
-      <c r="C24" s="32">
+      <c r="A24" s="32"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="13">
         <v>12</v>
       </c>
-      <c r="D24" s="33" t="s">
+      <c r="D24" s="14" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="29"/>
-      <c r="B25" s="26"/>
-      <c r="C25" s="32">
+      <c r="A25" s="32"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="13">
         <v>13</v>
       </c>
-      <c r="D25" s="33" t="s">
+      <c r="D25" s="14" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="29"/>
-      <c r="B26" s="26"/>
-      <c r="C26" s="32">
+      <c r="A26" s="32"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="13">
         <v>14</v>
       </c>
-      <c r="D26" s="32" t="s">
+      <c r="D26" s="13" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="29"/>
-      <c r="B27" s="26"/>
-      <c r="C27" s="32">
+      <c r="A27" s="32"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="13">
         <v>15</v>
       </c>
-      <c r="D27" s="32" t="s">
+      <c r="D27" s="13" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="29"/>
-      <c r="B28" s="26"/>
-      <c r="C28" s="32">
+      <c r="A28" s="32"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="13">
         <v>16</v>
       </c>
-      <c r="D28" s="32" t="s">
+      <c r="D28" s="13" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="29"/>
-      <c r="B29" s="26"/>
-      <c r="C29" s="32">
+      <c r="A29" s="32"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="13">
         <v>17</v>
       </c>
-      <c r="D29" s="32" t="s">
+      <c r="D29" s="13" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="29"/>
-      <c r="B30" s="26"/>
-      <c r="C30" s="32">
+      <c r="A30" s="32"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="13">
         <v>18</v>
       </c>
-      <c r="D30" s="32" t="s">
+      <c r="D30" s="13" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="29"/>
-      <c r="B31" s="26"/>
-      <c r="C31" s="32">
+      <c r="A31" s="32"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="13">
         <v>19</v>
       </c>
-      <c r="D31" s="32" t="s">
+      <c r="D31" s="13" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="29"/>
-      <c r="B32" s="26"/>
-      <c r="C32" s="32">
+      <c r="A32" s="32"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="13">
         <v>20</v>
       </c>
-      <c r="D32" s="32" t="s">
+      <c r="D32" s="13" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="29"/>
-      <c r="B33" s="26"/>
-      <c r="C33" s="32">
+      <c r="A33" s="32"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="13">
         <v>21</v>
       </c>
-      <c r="D33" s="32" t="s">
+      <c r="D33" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="29"/>
-      <c r="B34" s="26"/>
-      <c r="C34" s="32">
+      <c r="A34" s="32"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="13">
         <v>22</v>
       </c>
-      <c r="D34" s="32" t="s">
+      <c r="D34" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="29"/>
-      <c r="B35" s="26"/>
-      <c r="C35" s="32">
+      <c r="A35" s="32"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="13">
         <v>23</v>
       </c>
-      <c r="D35" s="32" t="s">
+      <c r="D35" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="29"/>
-      <c r="B36" s="26"/>
-      <c r="C36" s="32">
+      <c r="A36" s="32"/>
+      <c r="B36" s="29"/>
+      <c r="C36" s="13">
         <v>24</v>
       </c>
-      <c r="D36" s="32" t="s">
+      <c r="D36" s="13" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="29"/>
-      <c r="B37" s="26"/>
-      <c r="C37" s="32">
+      <c r="A37" s="32"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="13">
         <v>25</v>
       </c>
-      <c r="D37" s="32" t="s">
+      <c r="D37" s="13" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="29"/>
-      <c r="B38" s="26"/>
-      <c r="C38" s="32">
+      <c r="A38" s="32"/>
+      <c r="B38" s="29"/>
+      <c r="C38" s="13">
         <v>26</v>
       </c>
-      <c r="D38" s="32" t="s">
+      <c r="D38" s="13" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="29"/>
-      <c r="B39" s="26"/>
-      <c r="C39" s="32">
+      <c r="A39" s="32"/>
+      <c r="B39" s="29"/>
+      <c r="C39" s="13">
         <v>27</v>
       </c>
-      <c r="D39" s="32" t="s">
+      <c r="D39" s="13" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="30"/>
-      <c r="B40" s="27"/>
-      <c r="C40" s="32">
+      <c r="A40" s="33"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="13">
         <v>28</v>
       </c>
-      <c r="D40" s="32" t="s">
+      <c r="D40" s="13" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C42" s="31" t="s">
+      <c r="C42" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D42" s="31" t="s">
+      <c r="D42" s="12" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="22" t="s">
+      <c r="A43" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="20" t="s">
+      <c r="B43" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="C43" s="32">
+      <c r="C43" s="13">
         <v>0</v>
       </c>
-      <c r="D43" s="32" t="s">
+      <c r="D43" s="13" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="23"/>
-      <c r="B44" s="20"/>
-      <c r="C44" s="32">
+      <c r="A44" s="27"/>
+      <c r="B44" s="24"/>
+      <c r="C44" s="13">
         <v>1</v>
       </c>
-      <c r="D44" s="32" t="s">
+      <c r="D44" s="13" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="24" t="s">
+      <c r="A45" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="B45" s="20"/>
-      <c r="C45" s="32">
+      <c r="B45" s="24"/>
+      <c r="C45" s="13">
         <v>0</v>
       </c>
-      <c r="D45" s="32" t="s">
+      <c r="D45" s="13" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="24"/>
-      <c r="B46" s="20"/>
-      <c r="C46" s="32">
+      <c r="A46" s="34"/>
+      <c r="B46" s="24"/>
+      <c r="C46" s="13">
         <v>1</v>
       </c>
-      <c r="D46" s="32" t="s">
+      <c r="D46" s="13" t="s">
         <v>54</v>
       </c>
     </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C48" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B49" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C49" s="13">
+        <v>0</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" s="26"/>
+      <c r="B50" s="24"/>
+      <c r="C50" s="13">
+        <v>1</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" s="27"/>
+      <c r="B51" s="24"/>
+      <c r="C51" s="13">
+        <v>2</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B43:B46"/>
-    <mergeCell ref="B13:B40"/>
-    <mergeCell ref="A13:A40"/>
+  <mergeCells count="9">
     <mergeCell ref="B3:B10"/>
     <mergeCell ref="A3:A10"/>
     <mergeCell ref="A43:A44"/>
     <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B49:B51"/>
+    <mergeCell ref="A49:A51"/>
+    <mergeCell ref="B43:B46"/>
+    <mergeCell ref="B13:B40"/>
+    <mergeCell ref="A13:A40"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
